--- a/5bus_New.xlsx
+++ b/5bus_New.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\USYD\Y3S2\ELEC4712\MAST-julia-main(5 Bus)\MAST-julia-main\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0022676E-A3CF-4CAB-BBFC-E8DFE0A08BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D135A1B-AE2B-40DE-AA8F-2CFF11602BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{609F6487-E44D-42E0-A32D-22F076EA5C19}"/>
+    <workbookView xWindow="768" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{609F6487-E44D-42E0-A32D-22F076EA5C19}"/>
   </bookViews>
   <sheets>
     <sheet name="Generator Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="93">
   <si>
     <t>Generator Name</t>
   </si>
@@ -296,9 +296,6 @@
     <t>Discharging Efficiency (%)</t>
   </si>
   <si>
-    <t>PV Battery</t>
-  </si>
-  <si>
     <t>Purple</t>
   </si>
   <si>
@@ -309,6 +306,18 @@
   </si>
   <si>
     <t>Black</t>
+  </si>
+  <si>
+    <t>VPP Battery</t>
+  </si>
+  <si>
+    <t>VPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L8 </t>
+  </si>
+  <si>
+    <t>L9</t>
   </si>
 </sst>
 </file>
@@ -760,7 +769,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -820,7 +829,7 @@
         <v>21</v>
       </c>
       <c r="T2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -922,11 +931,11 @@
         <v>1500</v>
       </c>
       <c r="L4">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>-900</v>
+        <v>-600</v>
       </c>
       <c r="N4">
         <v>210</v>
@@ -936,16 +945,16 @@
         <v>210</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T4" t="s">
         <v>26</v>
@@ -1023,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2AB2BC-91A9-471F-8888-8B16F641E482}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1108,7 +1117,7 @@
         <v>8.4000000000000003E-4</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F8" si="0">0.000084*10</f>
+        <f t="shared" ref="F3:F10" si="0">0.000084*10</f>
         <v>8.3999999999999993E-4</v>
       </c>
       <c r="G3">
@@ -1286,6 +1295,72 @@
         <v>62</v>
       </c>
       <c r="J8">
+        <v>0.6109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>8.4000000000000003E-4</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>8.3999999999999993E-4</v>
+      </c>
+      <c r="G9">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="H9">
+        <v>4700</v>
+      </c>
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9">
+        <v>0.6109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>8.4000000000000003E-4</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>8.3999999999999993E-4</v>
+      </c>
+      <c r="G10">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="H10">
+        <v>4700</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10">
         <v>0.6109</v>
       </c>
     </row>
@@ -1296,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE61A350-5A9C-4B07-98B5-B1E807144D5E}">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -1379,7 +1454,7 @@
       </c>
       <c r="C2" s="3"/>
       <c r="E2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -1427,10 +1502,10 @@
         <v>54</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>55</v>
@@ -1445,7 +1520,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="E3" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -1493,10 +1568,10 @@
         <v>54</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>55</v>
@@ -1511,7 +1586,7 @@
       </c>
       <c r="C4" s="3"/>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -1565,7 +1640,7 @@
       </c>
       <c r="C5" s="3"/>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1619,7 +1694,7 @@
       </c>
       <c r="C6" s="3"/>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1662,6 +1737,60 @@
       </c>
       <c r="S6" s="1" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" s="1" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>85</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="R7" s="1">
+        <v>330</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1709,25 +1838,25 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F2">
-        <v>20000</v>
+        <v>2500</v>
       </c>
       <c r="G2">
-        <v>20000</v>
+        <v>2500</v>
       </c>
       <c r="H2">
         <v>85</v>
@@ -1736,7 +1865,7 @@
         <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
